--- a/check_mainspef_tretspef_outpatient_GF.xlsx
+++ b/check_mainspef_tretspef_outpatient_GF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms0952_ox_ac_uk/Documents/CO-ACTION/Secondary care analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="8_{E9938ED5-5D46-40C8-9842-25AD983EF399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDD85E27-EAB0-4C0D-ACC0-C51C4B7C043B}"/>
+  <xr:revisionPtr revIDLastSave="247" documentId="8_{E9938ED5-5D46-40C8-9842-25AD983EF399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19B40A1B-E526-432B-B0CA-098D1C133D6C}"/>
   <bookViews>
-    <workbookView xWindow="37455" yWindow="2070" windowWidth="16770" windowHeight="11295" xr2:uid="{17CCA721-EAA2-4C47-BCCE-5CD3B6F352DA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{17CCA721-EAA2-4C47-BCCE-5CD3B6F352DA}"/>
   </bookViews>
   <sheets>
     <sheet name="mapping_mainspef_tretspef" sheetId="1" r:id="rId1"/>
@@ -823,6 +823,9 @@
     <t>perinatal mental health service</t>
   </si>
   <si>
+    <t>paediatric diabetic service</t>
+  </si>
+  <si>
     <t>paediatric oral and maxillofacial surgery service</t>
   </si>
   <si>
@@ -1712,9 +1715,6 @@
   </si>
   <si>
     <t>Obstetrics and Gynaecology (not used in HES)</t>
-  </si>
-  <si>
-    <t>paediatric diabetes service</t>
   </si>
 </sst>
 </file>
@@ -2281,7 +2281,17 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2650,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2687,7 +2697,7 @@
         <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E3">
         <v>101</v>
@@ -2936,7 +2946,7 @@
         <v>76</v>
       </c>
       <c r="B18" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C18">
         <v>145</v>
@@ -2959,7 +2969,7 @@
         <v>150</v>
       </c>
       <c r="D19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E19">
         <v>150</v>
@@ -3072,7 +3082,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C26">
         <v>340</v>
@@ -3231,7 +3241,7 @@
         <v>420</v>
       </c>
       <c r="D35" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E35">
         <v>217</v>
@@ -3384,7 +3394,7 @@
         <v>420</v>
       </c>
       <c r="D44" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E44">
         <v>254</v>
@@ -3503,7 +3513,7 @@
         <v>420</v>
       </c>
       <c r="D51" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E51">
         <v>261</v>
@@ -3519,8 +3529,8 @@
       <c r="C52">
         <v>420</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>558</v>
+      <c r="D52" t="s">
+        <v>261</v>
       </c>
       <c r="E52">
         <v>263</v>
@@ -3571,7 +3581,7 @@
         <v>600</v>
       </c>
       <c r="D55" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E55">
         <v>300</v>
@@ -3588,7 +3598,7 @@
         <v>710</v>
       </c>
       <c r="D56" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E56">
         <v>710</v>
@@ -3616,7 +3626,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C58">
         <v>302</v>
@@ -3701,13 +3711,13 @@
         <v>42</v>
       </c>
       <c r="B63" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C63">
         <v>302</v>
       </c>
       <c r="D63" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E63">
         <v>307</v>
@@ -3792,7 +3802,7 @@
         <v>314</v>
       </c>
       <c r="D68" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E68">
         <v>314</v>
@@ -3843,7 +3853,7 @@
         <v>317</v>
       </c>
       <c r="D71" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E71">
         <v>317</v>
@@ -3939,7 +3949,7 @@
         <v>205</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C77" s="5">
         <v>833</v>
@@ -4109,7 +4119,7 @@
         <v>142</v>
       </c>
       <c r="B87" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C87">
         <v>340</v>
@@ -4126,7 +4136,7 @@
         <v>169</v>
       </c>
       <c r="B88" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C88">
         <v>340</v>
@@ -4211,13 +4221,13 @@
         <v>37</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C93" s="5">
         <v>361</v>
       </c>
       <c r="D93" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E93">
         <v>361</v>
@@ -4268,7 +4278,7 @@
         <v>400</v>
       </c>
       <c r="D96" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E96">
         <v>400</v>
@@ -4387,7 +4397,7 @@
         <v>430</v>
       </c>
       <c r="D103" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E103">
         <v>430</v>
@@ -4608,7 +4618,7 @@
         <v>960</v>
       </c>
       <c r="D116" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E116">
         <v>654</v>
@@ -4676,7 +4686,7 @@
         <v>130</v>
       </c>
       <c r="D120" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E120">
         <v>658</v>
@@ -4925,7 +4935,7 @@
         <v>143</v>
       </c>
       <c r="B135" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C135">
         <v>810</v>
@@ -4942,7 +4952,7 @@
         <v>7</v>
       </c>
       <c r="B136" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C136">
         <v>810</v>
@@ -4976,7 +4986,7 @@
         <v>80</v>
       </c>
       <c r="B138" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C138">
         <v>310</v>
@@ -4993,7 +5003,7 @@
         <v>39</v>
       </c>
       <c r="B139" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C139">
         <v>310</v>
@@ -5060,18 +5070,18 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C2" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D2" s="7">
         <v>326</v>
@@ -5079,7 +5089,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C3" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D3" s="7">
         <v>721</v>
@@ -5087,7 +5097,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C4" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D4" s="7">
         <v>343</v>
@@ -5095,7 +5105,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C5" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D5" s="7">
         <v>710</v>
@@ -5103,13 +5113,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B6" s="5">
         <v>902</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D6" s="7">
         <v>317</v>
@@ -5117,13 +5127,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B7" s="5">
         <v>710</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D7" s="7">
         <v>190</v>
@@ -5131,7 +5141,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C8" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D8" s="7">
         <v>324</v>
@@ -5139,7 +5149,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C9" s="6" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D9" s="7">
         <v>660</v>
@@ -5147,13 +5157,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B10" s="5">
         <v>831</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D10" s="7">
         <v>310</v>
@@ -5161,7 +5171,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C11" s="6" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D11" s="7">
         <v>840</v>
@@ -5169,13 +5179,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B12" s="5">
         <v>712</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D12" s="7">
         <v>200</v>
@@ -5183,13 +5193,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B13" s="5">
         <v>143</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D13" s="7">
         <v>109</v>
@@ -5197,13 +5207,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B14" s="5">
         <v>824</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D14" s="7">
         <v>308</v>
@@ -5211,13 +5221,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B15" s="5">
         <v>110</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D15" s="7">
         <v>103</v>
@@ -5225,13 +5235,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B16" s="5">
         <v>200</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D16" s="7">
         <v>161</v>
@@ -5239,7 +5249,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C17" s="6" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D17" s="7">
         <v>675</v>
@@ -5247,7 +5257,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C18" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D18" s="7">
         <v>327</v>
@@ -5255,13 +5265,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B19" s="5">
         <v>301</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D19" s="7">
         <v>172</v>
@@ -5269,13 +5279,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B20" s="5">
         <v>950</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D20" s="7">
         <v>320</v>
@@ -5283,13 +5293,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B21" s="5">
         <v>300</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D21" s="7">
         <v>170</v>
@@ -5297,13 +5307,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B22" s="5">
         <v>303</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D22" s="7">
         <v>174</v>
@@ -5311,7 +5321,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C23" s="6" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D23" s="7">
         <v>822</v>
@@ -5319,7 +5329,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C24" s="6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D24" s="7">
         <v>711</v>
@@ -5327,13 +5337,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B25" s="5">
         <v>832</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D25" s="7">
         <v>311</v>
@@ -5341,13 +5351,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B26" s="5">
         <v>810</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D26" s="7">
         <v>303</v>
@@ -5355,13 +5365,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B27" s="5">
         <v>833</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D27" s="7">
         <v>313</v>
@@ -5369,13 +5379,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B28" s="5">
         <v>901</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D28" s="7">
         <v>316</v>
@@ -5383,13 +5393,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B29" s="5">
         <v>960</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D29" s="7">
         <v>322</v>
@@ -5397,7 +5407,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C30" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D30" s="7">
         <v>401</v>
@@ -5405,7 +5415,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C31" s="6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D31" s="7">
         <v>800</v>
@@ -5413,13 +5423,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B32" s="5">
         <v>821</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D32" s="7">
         <v>305</v>
@@ -5427,13 +5437,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B33" s="5">
         <v>820</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D33" s="7">
         <v>304</v>
@@ -5441,7 +5451,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C34" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D34" s="7">
         <v>656</v>
@@ -5449,13 +5459,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B35" s="5">
         <v>120</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D35" s="7">
         <v>104</v>
@@ -5463,13 +5473,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B36" s="5">
         <v>600</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D36" s="7">
         <v>290</v>
@@ -5477,7 +5487,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C37" s="6" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D37" s="7">
         <v>504</v>
@@ -5485,7 +5495,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C38" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D38" s="7">
         <v>344</v>
@@ -5493,7 +5503,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C39" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D39" s="7">
         <v>331</v>
@@ -5501,7 +5511,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C40" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D40" s="7">
         <v>727</v>
@@ -5509,7 +5519,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C41" s="6" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D41" s="7">
         <v>450</v>
@@ -5517,7 +5527,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C42" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D42" s="7">
         <v>330</v>
@@ -5525,13 +5535,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B43" s="5">
         <v>823</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D43" s="7">
         <v>307</v>
@@ -5539,7 +5549,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C44" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D44" s="7">
         <v>920</v>
@@ -5547,7 +5557,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C45" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D45" s="7">
         <v>812</v>
@@ -5555,7 +5565,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C46" s="6" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D46" s="7">
         <v>654</v>
@@ -5563,7 +5573,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C47" s="6" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D47" s="7">
         <v>659</v>
@@ -5571,13 +5581,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B48" s="5">
         <v>149</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D48" s="7">
         <v>120</v>
@@ -5585,7 +5595,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C49" s="6" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D49" s="7">
         <v>720</v>
@@ -5593,7 +5603,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C50" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D50" s="7">
         <v>430</v>
@@ -5601,13 +5611,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B51" s="5">
         <v>700</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D51" s="7">
         <v>180</v>
@@ -5615,13 +5625,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B52" s="5">
         <v>147</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D52" s="7">
         <v>113</v>
@@ -5629,13 +5639,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B53" s="5">
         <v>800</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D53" s="7">
         <v>302</v>
@@ -5643,7 +5653,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C54" s="6" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D54" s="7">
         <v>505</v>
@@ -5651,7 +5661,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C55" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D55" s="7">
         <v>712</v>
@@ -5659,13 +5669,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B56" s="5">
         <v>715</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D56" s="7">
         <v>301</v>
@@ -5673,7 +5683,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C57" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D57" s="7">
         <v>677</v>
@@ -5681,13 +5691,13 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B58" s="5">
         <v>713</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D58" s="7">
         <v>300</v>
@@ -5695,13 +5705,13 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B59" s="5">
         <v>100</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D59" s="7">
         <v>100</v>
@@ -5709,7 +5719,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C60" s="6" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D60" s="7">
         <v>360</v>
@@ -5717,7 +5727,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C61" s="6" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D61" s="7">
         <v>503</v>
@@ -5725,7 +5735,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C62" s="6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D62" s="7">
         <v>502</v>
@@ -5733,13 +5743,13 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B63" s="5">
         <v>830</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D63" s="7">
         <v>309</v>
@@ -5747,13 +5757,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B64" s="5">
         <v>130</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D64" s="7">
         <v>105</v>
@@ -5761,13 +5771,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B65" s="5">
         <v>822</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D65" s="7">
         <v>306</v>
@@ -5775,7 +5785,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C66" s="6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D66" s="7">
         <v>350</v>
@@ -5783,7 +5793,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C67" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D67" s="7">
         <v>335</v>
@@ -5791,13 +5801,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B68" s="5">
         <v>711</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D68" s="7">
         <v>192</v>
@@ -5805,13 +5815,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B69" s="5">
         <v>903</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D69" s="7">
         <v>318</v>
@@ -5819,7 +5829,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C70" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D70" s="7">
         <v>811</v>
@@ -5827,7 +5837,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C71" s="6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D71" s="7">
         <v>700</v>
@@ -5835,7 +5845,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C72" s="6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D72" s="7">
         <v>722</v>
@@ -5843,7 +5853,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C73" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D73" s="7">
         <v>346</v>
@@ -5851,13 +5861,13 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B74" s="5">
         <v>191</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D74" s="7">
         <v>144</v>
@@ -5865,7 +5875,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C75" s="6" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D75" s="7">
         <v>370</v>
@@ -5873,7 +5883,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C76" s="6" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D76" s="7">
         <v>460</v>
@@ -5881,7 +5891,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C77" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D77" s="7">
         <v>713</v>
@@ -5889,7 +5899,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C78" s="6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D78" s="7">
         <v>834</v>
@@ -5897,7 +5907,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C79" s="6" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D79" s="7">
         <v>726</v>
@@ -5905,7 +5915,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C80" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D80" s="7">
         <v>725</v>
@@ -5913,7 +5923,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C81" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D81" s="7">
         <v>560</v>
@@ -5921,7 +5931,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C82" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D82" s="7">
         <v>661</v>
@@ -5929,7 +5939,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C83" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D83" s="7">
         <v>422</v>
@@ -5937,7 +5947,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C84" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D84" s="7">
         <v>400</v>
@@ -5945,7 +5955,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C85" s="6" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D85" s="7">
         <v>730</v>
@@ -5953,13 +5963,13 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B86" s="5">
         <v>190</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D86" s="7">
         <v>150</v>
@@ -5967,7 +5977,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C87" s="6" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D87" s="7">
         <v>371</v>
@@ -5975,7 +5985,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C88" s="6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D88" s="7">
         <v>501</v>
@@ -5983,7 +5993,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C89" s="6" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D89" s="7">
         <v>651</v>
@@ -5991,7 +6001,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C90" s="6" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D90" s="7">
         <v>715</v>
@@ -5999,7 +6009,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C91" s="6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D91" s="7">
         <v>461</v>
@@ -6007,13 +6017,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B92" s="5">
         <v>150</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D92" s="7">
         <v>130</v>
@@ -6021,7 +6031,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C93" s="6" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D93" s="7">
         <v>662</v>
@@ -6029,13 +6039,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B94" s="5">
         <v>180</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D94" s="7">
         <v>145</v>
@@ -6043,13 +6053,13 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B95" s="5">
         <v>160</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D95" s="7">
         <v>140</v>
@@ -6057,13 +6067,13 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B96" s="5">
         <v>171</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D96" s="7">
         <v>143</v>
@@ -6071,7 +6081,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C97" s="6" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D97" s="7">
         <v>431</v>
@@ -6079,13 +6089,13 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B98" s="5">
         <v>146</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D98" s="7">
         <v>111</v>
@@ -6093,7 +6103,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C99" s="6" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D99" s="7">
         <v>655</v>
@@ -6101,7 +6111,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C100" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D100" s="7">
         <v>658</v>
@@ -6109,13 +6119,13 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B101" s="5">
         <v>420</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D101" s="7">
         <v>254</v>
@@ -6123,13 +6133,13 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B102" s="5">
         <v>326</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D102" s="7">
         <v>220</v>
@@ -6137,13 +6147,13 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B103" s="5">
         <v>330</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D103" s="7">
         <v>221</v>
@@ -6151,13 +6161,13 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B104" s="5">
         <v>610</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D104" s="7">
         <v>321</v>
@@ -6165,13 +6175,13 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B105" s="5">
         <v>410</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D105" s="7">
         <v>253</v>
@@ -6179,13 +6189,13 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B106" s="5">
         <v>421</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D106" s="7">
         <v>255</v>
@@ -6193,13 +6203,13 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B107" s="5">
         <v>352</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D107" s="7">
         <v>230</v>
@@ -6207,13 +6217,13 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B108" s="5">
         <v>510</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D108" s="7">
         <v>264</v>
@@ -6221,13 +6231,13 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B109" s="5">
         <v>305</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D109" s="7">
         <v>142</v>
@@ -6235,13 +6245,13 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B110" s="5">
         <v>450</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D110" s="7">
         <v>257</v>
@@ -6249,13 +6259,13 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B111" s="5">
         <v>504</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D111" s="7">
         <v>263</v>
@@ -6263,13 +6273,13 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B112" s="5">
         <v>315</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D112" s="7">
         <v>215</v>
@@ -6277,13 +6287,13 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B113" s="5">
         <v>520</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D113" s="7">
         <v>270</v>
@@ -6291,13 +6301,13 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B114" s="5">
         <v>401</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D114" s="7">
         <v>252</v>
@@ -6305,13 +6315,13 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B115" s="5">
         <v>350</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D115" s="7">
         <v>223</v>
@@ -6319,13 +6329,13 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B116" s="5">
         <v>400</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D116" s="7">
         <v>251</v>
@@ -6333,13 +6343,13 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B117" s="5">
         <v>313</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D117" s="7">
         <v>213</v>
@@ -6347,13 +6357,13 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B118" s="5">
         <v>371</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D118" s="7">
         <v>250</v>
@@ -6361,13 +6371,13 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B119" s="5">
         <v>430</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D119" s="7">
         <v>256</v>
@@ -6375,13 +6385,13 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B120" s="5">
         <v>501</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D120" s="7">
         <v>261</v>
@@ -6389,13 +6399,13 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B121" s="5">
         <v>370</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D121" s="7">
         <v>242</v>
@@ -6403,13 +6413,13 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B122" s="5">
         <v>560</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D122" s="7">
         <v>280</v>
@@ -6417,13 +6427,13 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B123" s="5">
         <v>500</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D123" s="7">
         <v>260</v>
@@ -6431,13 +6441,13 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B124" s="5">
         <v>460</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D124" s="7">
         <v>259</v>
@@ -6445,13 +6455,13 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B125" s="5">
         <v>601</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D125" s="7">
         <v>291</v>
@@ -6459,13 +6469,13 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B126" s="5">
         <v>620</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D126" s="7">
         <v>421</v>
@@ -6473,13 +6483,13 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B127" s="5">
         <v>321</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D127" s="7">
         <v>218</v>
@@ -6487,13 +6497,13 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B128" s="5">
         <v>317</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D128" s="7">
         <v>216</v>
@@ -6501,13 +6511,13 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B129" s="5">
         <v>320</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D129" s="7">
         <v>217</v>
@@ -6515,13 +6525,13 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B130" s="5">
         <v>361</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D130" s="7">
         <v>241</v>
@@ -6529,13 +6539,13 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B131" s="5">
         <v>360</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D131" s="7">
         <v>240</v>
@@ -6543,13 +6553,13 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B132" s="5">
         <v>325</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D132" s="7">
         <v>219</v>
@@ -6557,13 +6567,13 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B133" s="5">
         <v>451</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D133" s="7">
         <v>258</v>
@@ -6571,13 +6581,13 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B134" s="5">
         <v>502</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D134" s="7">
         <v>262</v>
@@ -6585,7 +6595,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C135" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D135" s="7">
         <v>420</v>
@@ -6593,13 +6603,13 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B136" s="5">
         <v>310</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D136" s="7">
         <v>171</v>
@@ -6607,13 +6617,13 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B137" s="5">
         <v>340</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D137" s="7">
         <v>222</v>
@@ -6621,13 +6631,13 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B138" s="5">
         <v>312</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D138" s="7">
         <v>212</v>
@@ -6635,13 +6645,13 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B139" s="5">
         <v>314</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D139" s="7">
         <v>214</v>
@@ -6649,13 +6659,13 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B140" s="5">
         <v>311</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D140" s="7">
         <v>211</v>
@@ -6663,13 +6673,13 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B141" s="5">
         <v>304</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D141" s="7">
         <v>191</v>
@@ -6677,13 +6687,13 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B142" s="5">
         <v>900</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D142" s="7">
         <v>315</v>
@@ -6691,7 +6701,7 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C143" s="6" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D143" s="7">
         <v>724</v>
@@ -6699,7 +6709,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C144" s="6" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D144" s="7">
         <v>650</v>
@@ -6707,13 +6717,13 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B145" s="5">
         <v>192</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D145" s="7">
         <v>160</v>
@@ -6721,7 +6731,7 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C146" s="6" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D146" s="7">
         <v>663</v>
@@ -6729,7 +6739,7 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C147" s="6" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D147" s="7">
         <v>653</v>
@@ -6737,7 +6747,7 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C148" s="6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D148" s="7">
         <v>348</v>
@@ -6745,7 +6755,7 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C149" s="6" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D149" s="7">
         <v>657</v>
@@ -6753,7 +6763,7 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C150" s="6" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D150" s="7">
         <v>723</v>
@@ -6761,7 +6771,7 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C151" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D151" s="7">
         <v>342</v>
@@ -6769,7 +6779,7 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C152" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D152" s="7">
         <v>333</v>
@@ -6777,13 +6787,13 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B153" s="5">
         <v>834</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D153" s="7">
         <v>314</v>
@@ -6791,7 +6801,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C154" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D154" s="7">
         <v>361</v>
@@ -6799,7 +6809,7 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C155" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D155" s="7">
         <v>340</v>
@@ -6807,7 +6817,7 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C156" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D156" s="7">
         <v>341</v>
@@ -6815,13 +6825,13 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B157" s="5">
         <v>904</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D157" s="7">
         <v>319</v>
@@ -6835,7 +6845,7 @@
         <v>170</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D158" s="7">
         <v>141</v>
@@ -6843,7 +6853,7 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C159" s="6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D159" s="7">
         <v>510</v>
@@ -6851,7 +6861,7 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C160" s="6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D160" s="7">
         <v>520</v>
@@ -6859,7 +6869,7 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C161" s="6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D161" s="7">
         <v>610</v>
@@ -6867,7 +6877,7 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C162" s="6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D162" s="7">
         <v>620</v>
@@ -6875,7 +6885,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C163" s="6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D163" s="7">
         <v>832</v>
@@ -6883,7 +6893,7 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C164" s="6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D164" s="7">
         <v>990</v>
@@ -6891,7 +6901,7 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C165" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D165" s="7">
         <v>410</v>
@@ -6899,7 +6909,7 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C166" s="6" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D166" s="7">
         <v>347</v>
@@ -6907,7 +6917,7 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C167" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D167" s="7">
         <v>451</v>
@@ -6915,7 +6925,7 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C168" s="6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D168" s="7">
         <v>345</v>
@@ -6923,7 +6933,7 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C169" s="6" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D169" s="7">
         <v>652</v>
@@ -6931,13 +6941,13 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B170" s="5">
         <v>990</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D170" s="7">
         <v>323</v>
@@ -6945,13 +6955,13 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B171" s="5">
         <v>142</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D171" s="7">
         <v>108</v>
@@ -6959,7 +6969,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C172" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D172" s="7">
         <v>325</v>
@@ -6967,7 +6977,7 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C173" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D173" s="7">
         <v>328</v>
@@ -6975,13 +6985,13 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B174" s="5">
         <v>302</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D174" s="7">
         <v>173</v>
@@ -6989,7 +6999,7 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C175" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D175" s="7">
         <v>329</v>
@@ -6997,13 +7007,13 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B176" s="5">
         <v>107</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D176" s="7">
         <v>102</v>
@@ -7011,13 +7021,13 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B177" s="5">
         <v>145</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D177" s="7">
         <v>110</v>
@@ -7025,13 +7035,13 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B178" s="5">
         <v>148</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D178" s="7">
         <v>115</v>
@@ -7039,7 +7049,7 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C179" s="6" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D179" s="7">
         <v>352</v>
@@ -7047,13 +7057,13 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B180" s="5">
         <v>140</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D180" s="7">
         <v>106</v>
@@ -7061,7 +7071,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C181" s="6" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D181" s="7">
         <v>670</v>
@@ -7069,13 +7079,13 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B182" s="5">
         <v>101</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D182" s="7">
         <v>101</v>
@@ -7083,7 +7093,7 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C183" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D183" s="7">
         <v>673</v>
@@ -7091,13 +7101,13 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B184" s="5">
         <v>141</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D184" s="7">
         <v>107</v>
@@ -7105,7 +7115,7 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C185" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D185" s="7">
         <v>424</v>
@@ -7118,7 +7128,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
